--- a/reports/livrables/L4_analyse/offre_tableaux.xlsx
+++ b/reports/livrables/L4_analyse/offre_tableaux.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verdicts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canaux" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolution_magasins" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lancements" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Age_des_produits" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decomposition_magasins" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memes_produits" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indice1_rotation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indice2_dispersion" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indice3_pays" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indice4_retour" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gammes_de_prix" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entree_de_gamme" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entree_de_gamme_memes_prod" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entree_de_gamme_trimestres" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients_statut" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients_pays" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients_nouveautes" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Verdicts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Canaux" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Evolution_magasins" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Categories" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lancements" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Age_des_produits" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Decomposition_magasins" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Memes_produits" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Indice1_rotation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Indice2_dispersion" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Indice3_pays" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Indice4_retour" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Gammes_de_prix" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Entree_de_gamme" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Entree_de_gamme_memes_prod" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Entree_de_gamme_trimestres" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Clients_statut" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Clients_pays" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Clients_nouveautes" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
